--- a/docs/StructureDefinition-DIPSLocation.xlsx
+++ b/docs/StructureDefinition-DIPSLocation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:16:58+00:00</t>
+    <t>2026-09-08T11:30:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -439,7 +439,7 @@
     <t>validPeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/LocationValidPeriod}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/Location-validPeriod}
 </t>
   </si>
   <si>
@@ -459,7 +459,7 @@
     <t>labLocalizationId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/LocationLabLocalizationId}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/Location-labLocalizationId}
 </t>
   </si>
   <si>
@@ -469,7 +469,7 @@
     <t>workplaceLocalizationId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/LocationWorkplaceLocalizationId}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/Location-workplaceLocalizationId}
 </t>
   </si>
   <si>
@@ -1356,7 +1356,7 @@
     <t>locationTypeId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/LocationTypeId}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/LocationTypeId}
 </t>
   </si>
   <si>
@@ -1387,7 +1387,7 @@
     <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/LocationTypeId</t>
+    <t>http://DIPS.no/fhir/StructureDefinition/R4/LocationTypeId</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -1501,7 +1501,7 @@
     <t>bedtypeId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/BedTypeId}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/BedTypeId}
 </t>
   </si>
   <si>
@@ -1514,7 +1514,7 @@
     <t>Location.type:BedType.coding.extension:bedtypeId.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/BedTypeId</t>
+    <t>http://DIPS.no/fhir/StructureDefinition/R4/BedTypeId</t>
   </si>
   <si>
     <t>Location.type:BedType.coding.extension:bedtypeId.value[x]</t>
@@ -1592,7 +1592,7 @@
     <t>teamTypeId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/TeamTypeId}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/TeamTypeId}
 </t>
   </si>
   <si>
@@ -1605,7 +1605,7 @@
     <t>Location.type:TeamType.coding.extension:teamTypeId.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/TeamTypeId</t>
+    <t>http://DIPS.no/fhir/StructureDefinition/R4/TeamTypeId</t>
   </si>
   <si>
     <t>Location.type:TeamType.coding.extension:teamTypeId.value[x]</t>
@@ -1725,7 +1725,7 @@
     <t>wardTypeCodeId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/WardTypeCodeId}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/WardTypeCodeId}
 </t>
   </si>
   <si>
@@ -1738,7 +1738,7 @@
     <t>Location.type:WardType.coding.extension:wardTypeCodeId.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/WardTypeCodeId</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/WardTypeCodeId</t>
   </si>
   <si>
     <t>Location.type:WardType.coding.extension:wardTypeCodeId.value[x]</t>
@@ -1932,7 +1932,7 @@
     <t>addressId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/LocationAddressId}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/Location-addressId}
 </t>
   </si>
   <si>
@@ -2917,7 +2917,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="69.20703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="69.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-DIPSLocation.xlsx
+++ b/docs/StructureDefinition-DIPSLocation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:30:20+00:00</t>
+    <t>2026-09-15T05:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSLocation.xlsx
+++ b/docs/StructureDefinition-DIPSLocation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9901" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9901" uniqueCount="831">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T05:06:55+00:00</t>
+    <t>2026-09-17T19:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1892,10 +1892,20 @@
 </t>
   </si>
   <si>
+    <t>The concept of an officially registered address</t>
+  </si>
+  <si>
+    <t>Defines the concept of an officially registered address in Norway. Usually this will be the adress registered in "Folkeregisteret" for persons or "Enhetsregisteret" for organizations.</t>
+  </si>
+  <si>
     <t>Location.address.extension:urbanDistrict</t>
   </si>
   <si>
     <t>urbanDistrict</t>
+  </si>
+  <si>
+    <t>bydel
+urban district</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://hl7.no/fhir/StructureDefinition/no-basis-urban-district}
@@ -27514,7 +27524,7 @@
         <v>74</v>
       </c>
       <c r="G228" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H228" t="s" s="2">
         <v>73</v>
@@ -27529,10 +27539,10 @@
         <v>604</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>128</v>
+        <v>605</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>129</v>
+        <v>606</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -27606,16 +27616,16 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>600</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D229" t="s" s="2">
-        <v>73</v>
+        <v>609</v>
       </c>
       <c r="E229" s="2"/>
       <c r="F229" t="s" s="2">
@@ -27634,13 +27644,13 @@
         <v>73</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -27714,13 +27724,13 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>600</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D230" t="s" s="2">
         <v>73</v>
@@ -27742,13 +27752,13 @@
         <v>73</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
@@ -27822,13 +27832,13 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>600</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D231" t="s" s="2">
         <v>73</v>
@@ -27850,7 +27860,7 @@
         <v>73</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="L231" t="s" s="2">
         <v>137</v>
@@ -27930,10 +27940,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -27959,16 +27969,16 @@
         <v>102</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="O232" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="P232" t="s" s="2">
         <v>73</v>
@@ -27981,7 +27991,7 @@
         <v>73</v>
       </c>
       <c r="T232" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="U232" t="s" s="2">
         <v>73</v>
@@ -27996,10 +28006,10 @@
         <v>182</v>
       </c>
       <c r="Y232" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="Z232" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>73</v>
@@ -28017,7 +28027,7 @@
         <v>73</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>74</v>
@@ -28032,7 +28042,7 @@
         <v>94</v>
       </c>
       <c r="AK232" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AL232" t="s" s="2">
         <v>73</v>
@@ -28040,10 +28050,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -28069,13 +28079,13 @@
         <v>102</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="O233" s="2"/>
       <c r="P233" t="s" s="2">
@@ -28089,7 +28099,7 @@
         <v>73</v>
       </c>
       <c r="T233" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="U233" t="s" s="2">
         <v>73</v>
@@ -28104,10 +28114,10 @@
         <v>182</v>
       </c>
       <c r="Y233" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="Z233" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>73</v>
@@ -28125,7 +28135,7 @@
         <v>73</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>74</v>
@@ -28140,7 +28150,7 @@
         <v>94</v>
       </c>
       <c r="AK233" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AL233" t="s" s="2">
         <v>73</v>
@@ -28148,10 +28158,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -28177,16 +28187,16 @@
         <v>165</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="O234" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>73</v>
@@ -28199,7 +28209,7 @@
         <v>73</v>
       </c>
       <c r="T234" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="U234" t="s" s="2">
         <v>73</v>
@@ -28235,7 +28245,7 @@
         <v>73</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>74</v>
@@ -28250,7 +28260,7 @@
         <v>94</v>
       </c>
       <c r="AK234" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="AL234" t="s" s="2">
         <v>73</v>
@@ -28258,10 +28268,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -28287,10 +28297,10 @@
         <v>165</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" s="2"/>
@@ -28305,7 +28315,7 @@
         <v>73</v>
       </c>
       <c r="T235" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="U235" t="s" s="2">
         <v>73</v>
@@ -28341,7 +28351,7 @@
         <v>73</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>74</v>
@@ -28356,7 +28366,7 @@
         <v>94</v>
       </c>
       <c r="AK235" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="AL235" t="s" s="2">
         <v>73</v>
@@ -28364,14 +28374,14 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="E236" s="2"/>
       <c r="F236" t="s" s="2">
@@ -28393,10 +28403,10 @@
         <v>165</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
@@ -28411,7 +28421,7 @@
         <v>73</v>
       </c>
       <c r="T236" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="U236" t="s" s="2">
         <v>73</v>
@@ -28447,7 +28457,7 @@
         <v>73</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>74</v>
@@ -28462,7 +28472,7 @@
         <v>94</v>
       </c>
       <c r="AK236" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="AL236" t="s" s="2">
         <v>73</v>
@@ -28470,14 +28480,14 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="E237" s="2"/>
       <c r="F237" t="s" s="2">
@@ -28499,13 +28509,13 @@
         <v>165</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="O237" s="2"/>
       <c r="P237" t="s" s="2">
@@ -28519,7 +28529,7 @@
         <v>73</v>
       </c>
       <c r="T237" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="U237" t="s" s="2">
         <v>73</v>
@@ -28555,7 +28565,7 @@
         <v>73</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>74</v>
@@ -28570,7 +28580,7 @@
         <v>94</v>
       </c>
       <c r="AK237" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="AL237" t="s" s="2">
         <v>73</v>
@@ -28578,10 +28588,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -28607,10 +28617,10 @@
         <v>165</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" s="2"/>
@@ -28684,10 +28694,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -28788,13 +28798,13 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="D240" t="s" s="2">
         <v>73</v>
@@ -28816,13 +28826,13 @@
         <v>73</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="N240" s="2"/>
       <c r="O240" s="2"/>
@@ -28882,13 +28892,13 @@
         <v>75</v>
       </c>
       <c r="AI240" t="s" s="2">
-        <v>73</v>
+        <v>139</v>
       </c>
       <c r="AJ240" t="s" s="2">
         <v>133</v>
       </c>
       <c r="AK240" t="s" s="2">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="AL240" t="s" s="2">
         <v>73</v>
@@ -28896,10 +28906,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -28925,10 +28935,10 @@
         <v>165</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" s="2"/>
@@ -28952,7 +28962,7 @@
         <v>73</v>
       </c>
       <c r="W241" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="X241" t="s" s="2">
         <v>73</v>
@@ -28979,7 +28989,7 @@
         <v>73</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>74</v>
@@ -29002,14 +29012,14 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E242" s="2"/>
       <c r="F242" t="s" s="2">
@@ -29031,10 +29041,10 @@
         <v>165</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
@@ -29085,7 +29095,7 @@
         <v>73</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>74</v>
@@ -29100,7 +29110,7 @@
         <v>94</v>
       </c>
       <c r="AK242" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="AL242" t="s" s="2">
         <v>73</v>
@@ -29108,14 +29118,14 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E243" s="2"/>
       <c r="F243" t="s" s="2">
@@ -29137,10 +29147,10 @@
         <v>165</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="N243" s="2"/>
       <c r="O243" s="2"/>
@@ -29155,7 +29165,7 @@
         <v>73</v>
       </c>
       <c r="T243" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="U243" t="s" s="2">
         <v>73</v>
@@ -29191,7 +29201,7 @@
         <v>73</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>74</v>
@@ -29206,7 +29216,7 @@
         <v>94</v>
       </c>
       <c r="AK243" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="AL243" t="s" s="2">
         <v>73</v>
@@ -29214,10 +29224,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -29243,13 +29253,13 @@
         <v>165</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="N244" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="O244" s="2"/>
       <c r="P244" t="s" s="2">
@@ -29299,7 +29309,7 @@
         <v>73</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>74</v>
@@ -29314,7 +29324,7 @@
         <v>94</v>
       </c>
       <c r="AK244" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="AL244" t="s" s="2">
         <v>73</v>
@@ -29322,10 +29332,10 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -29351,14 +29361,14 @@
         <v>218</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="N245" s="2"/>
       <c r="O245" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="P245" t="s" s="2">
         <v>73</v>
@@ -29371,7 +29381,7 @@
         <v>73</v>
       </c>
       <c r="T245" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="U245" t="s" s="2">
         <v>73</v>
@@ -29407,7 +29417,7 @@
         <v>73</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>74</v>
@@ -29422,7 +29432,7 @@
         <v>94</v>
       </c>
       <c r="AK245" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="AL245" t="s" s="2">
         <v>73</v>
@@ -29430,10 +29440,10 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -29459,14 +29469,14 @@
         <v>189</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="N246" s="2"/>
       <c r="O246" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="P246" t="s" s="2">
         <v>73</v>
@@ -29491,13 +29501,13 @@
         <v>73</v>
       </c>
       <c r="X246" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="Y246" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="Z246" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>73</v>
@@ -29515,7 +29525,7 @@
         <v>73</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>74</v>
@@ -29530,7 +29540,7 @@
         <v>94</v>
       </c>
       <c r="AK246" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="AL246" t="s" s="2">
         <v>376</v>
@@ -29538,10 +29548,10 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -29644,10 +29654,10 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -29752,10 +29762,10 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -29862,10 +29872,10 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -29968,10 +29978,10 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -30076,10 +30086,10 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -30121,7 +30131,7 @@
       </c>
       <c r="Q252" s="2"/>
       <c r="R252" t="s" s="2">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="S252" t="s" s="2">
         <v>73</v>
@@ -30186,10 +30196,10 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -30294,10 +30304,10 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -30402,10 +30412,10 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -30510,10 +30520,10 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -30620,10 +30630,10 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -30730,10 +30740,10 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -30756,17 +30766,17 @@
         <v>73</v>
       </c>
       <c r="K258" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="N258" s="2"/>
       <c r="O258" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="P258" t="s" s="2">
         <v>73</v>
@@ -30815,7 +30825,7 @@
         <v>73</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>74</v>
@@ -30830,7 +30840,7 @@
         <v>94</v>
       </c>
       <c r="AK258" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="AL258" t="s" s="2">
         <v>73</v>
@@ -30838,10 +30848,10 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -30944,10 +30954,10 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -31052,14 +31062,14 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="E261" s="2"/>
       <c r="F261" t="s" s="2">
@@ -31081,10 +31091,10 @@
         <v>127</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="M261" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="N261" t="s" s="2">
         <v>150</v>
@@ -31139,7 +31149,7 @@
         <v>73</v>
       </c>
       <c r="AF261" t="s" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="AG261" t="s" s="2">
         <v>74</v>
@@ -31162,10 +31172,10 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -31188,13 +31198,13 @@
         <v>73</v>
       </c>
       <c r="K262" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="N262" s="2"/>
       <c r="O262" s="2"/>
@@ -31245,7 +31255,7 @@
         <v>73</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>82</v>
@@ -31260,7 +31270,7 @@
         <v>94</v>
       </c>
       <c r="AK262" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="AL262" t="s" s="2">
         <v>73</v>
@@ -31268,10 +31278,10 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -31294,13 +31304,13 @@
         <v>73</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="N263" s="2"/>
       <c r="O263" s="2"/>
@@ -31351,7 +31361,7 @@
         <v>73</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>82</v>
@@ -31366,7 +31376,7 @@
         <v>94</v>
       </c>
       <c r="AK263" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="AL263" t="s" s="2">
         <v>73</v>
@@ -31374,10 +31384,10 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -31400,13 +31410,13 @@
         <v>73</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="N264" s="2"/>
       <c r="O264" s="2"/>
@@ -31457,7 +31467,7 @@
         <v>73</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>74</v>
@@ -31472,7 +31482,7 @@
         <v>94</v>
       </c>
       <c r="AK264" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="AL264" t="s" s="2">
         <v>73</v>
@@ -31480,10 +31490,10 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -31506,19 +31516,19 @@
         <v>83</v>
       </c>
       <c r="K265" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="L265" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="M265" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="N265" t="s" s="2">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="O265" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="P265" t="s" s="2">
         <v>73</v>
@@ -31567,7 +31577,7 @@
         <v>73</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>74</v>
@@ -31582,7 +31592,7 @@
         <v>94</v>
       </c>
       <c r="AK265" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="AL265" t="s" s="2">
         <v>73</v>
@@ -31590,10 +31600,10 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -31696,10 +31706,10 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -31804,10 +31814,10 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -31833,13 +31843,13 @@
         <v>165</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="N268" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="O268" s="2"/>
       <c r="P268" t="s" s="2">
@@ -31889,7 +31899,7 @@
         <v>73</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>74</v>
@@ -31898,7 +31908,7 @@
         <v>82</v>
       </c>
       <c r="AI268" t="s" s="2">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="AJ268" t="s" s="2">
         <v>94</v>
@@ -31912,10 +31922,10 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -31941,13 +31951,13 @@
         <v>96</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="N269" t="s" s="2">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="O269" s="2"/>
       <c r="P269" t="s" s="2">
@@ -31976,10 +31986,10 @@
         <v>194</v>
       </c>
       <c r="Y269" t="s" s="2">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="Z269" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="AA269" t="s" s="2">
         <v>73</v>
@@ -31997,7 +32007,7 @@
         <v>73</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>74</v>
@@ -32020,10 +32030,10 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -32049,13 +32059,13 @@
         <v>154</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="N270" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="O270" s="2"/>
       <c r="P270" t="s" s="2">
@@ -32105,7 +32115,7 @@
         <v>73</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>74</v>
@@ -32120,7 +32130,7 @@
         <v>94</v>
       </c>
       <c r="AK270" t="s" s="2">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="AL270" t="s" s="2">
         <v>73</v>
@@ -32128,10 +32138,10 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -32234,10 +32244,10 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -32342,10 +32352,10 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -32452,10 +32462,10 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -32562,10 +32572,10 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -32607,7 +32617,7 @@
       </c>
       <c r="Q275" s="2"/>
       <c r="R275" t="s" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="S275" t="s" s="2">
         <v>73</v>
@@ -32672,10 +32682,10 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -32704,7 +32714,7 @@
         <v>210</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="N276" t="s" s="2">
         <v>212</v>
@@ -32780,10 +32790,10 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -32886,10 +32896,10 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -32994,10 +33004,10 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -33023,13 +33033,13 @@
         <v>165</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="N279" t="s" s="2">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="O279" s="2"/>
       <c r="P279" t="s" s="2">
@@ -33079,7 +33089,7 @@
         <v>73</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>74</v>
@@ -33102,10 +33112,10 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -33128,17 +33138,17 @@
         <v>73</v>
       </c>
       <c r="K280" t="s" s="2">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="M280" t="s" s="2">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="N280" s="2"/>
       <c r="O280" t="s" s="2">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="P280" t="s" s="2">
         <v>73</v>
@@ -33187,7 +33197,7 @@
         <v>73</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="AG280" t="s" s="2">
         <v>74</v>
@@ -33202,7 +33212,7 @@
         <v>94</v>
       </c>
       <c r="AK280" t="s" s="2">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="AL280" t="s" s="2">
         <v>73</v>
@@ -33210,10 +33220,10 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -33236,16 +33246,16 @@
         <v>73</v>
       </c>
       <c r="K281" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="N281" t="s" s="2">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="O281" s="2"/>
       <c r="P281" t="s" s="2">
@@ -33295,7 +33305,7 @@
         <v>73</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>74</v>
@@ -33310,7 +33320,7 @@
         <v>94</v>
       </c>
       <c r="AK281" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="AL281" t="s" s="2">
         <v>73</v>
@@ -33318,10 +33328,10 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -33424,10 +33434,10 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -33532,14 +33542,14 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="E284" s="2"/>
       <c r="F284" t="s" s="2">
@@ -33561,10 +33571,10 @@
         <v>127</v>
       </c>
       <c r="L284" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="M284" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="N284" t="s" s="2">
         <v>150</v>
@@ -33619,7 +33629,7 @@
         <v>73</v>
       </c>
       <c r="AF284" t="s" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="AG284" t="s" s="2">
         <v>74</v>
@@ -33642,10 +33652,10 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -33671,10 +33681,10 @@
         <v>102</v>
       </c>
       <c r="L285" t="s" s="2">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="M285" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="N285" s="2"/>
       <c r="O285" s="2"/>
@@ -33704,28 +33714,28 @@
         <v>182</v>
       </c>
       <c r="Y285" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="Z285" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="AA285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF285" t="s" s="2">
         <v>808</v>
-      </c>
-      <c r="Z285" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="AA285" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB285" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC285" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD285" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE285" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF285" t="s" s="2">
-        <v>805</v>
       </c>
       <c r="AG285" t="s" s="2">
         <v>74</v>
@@ -33740,7 +33750,7 @@
         <v>94</v>
       </c>
       <c r="AK285" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="AL285" t="s" s="2">
         <v>73</v>
@@ -33748,10 +33758,10 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -33777,10 +33787,10 @@
         <v>347</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="N286" s="2"/>
       <c r="O286" s="2"/>
@@ -33831,7 +33841,7 @@
         <v>73</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>74</v>
@@ -33846,7 +33856,7 @@
         <v>94</v>
       </c>
       <c r="AK286" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="AL286" t="s" s="2">
         <v>73</v>
@@ -33854,10 +33864,10 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -33880,13 +33890,13 @@
         <v>73</v>
       </c>
       <c r="K287" t="s" s="2">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="M287" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="N287" s="2"/>
       <c r="O287" s="2"/>
@@ -33937,7 +33947,7 @@
         <v>73</v>
       </c>
       <c r="AF287" t="s" s="2">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="AG287" t="s" s="2">
         <v>74</v>
@@ -33952,7 +33962,7 @@
         <v>94</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="AL287" t="s" s="2">
         <v>73</v>
@@ -33960,10 +33970,10 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -33986,13 +33996,13 @@
         <v>73</v>
       </c>
       <c r="K288" t="s" s="2">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="L288" t="s" s="2">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="M288" t="s" s="2">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="N288" s="2"/>
       <c r="O288" s="2"/>
@@ -34043,7 +34053,7 @@
         <v>73</v>
       </c>
       <c r="AF288" t="s" s="2">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="AG288" t="s" s="2">
         <v>74</v>
@@ -34058,7 +34068,7 @@
         <v>94</v>
       </c>
       <c r="AK288" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="AL288" t="s" s="2">
         <v>73</v>
@@ -34066,10 +34076,10 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -34095,10 +34105,10 @@
         <v>165</v>
       </c>
       <c r="L289" t="s" s="2">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="M289" t="s" s="2">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="N289" s="2"/>
       <c r="O289" s="2"/>
@@ -34149,7 +34159,7 @@
         <v>73</v>
       </c>
       <c r="AF289" t="s" s="2">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="AG289" t="s" s="2">
         <v>74</v>
@@ -34172,10 +34182,10 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -34198,17 +34208,17 @@
         <v>73</v>
       </c>
       <c r="K290" t="s" s="2">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="N290" s="2"/>
       <c r="O290" t="s" s="2">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="P290" t="s" s="2">
         <v>73</v>
@@ -34257,7 +34267,7 @@
         <v>73</v>
       </c>
       <c r="AF290" t="s" s="2">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="AG290" t="s" s="2">
         <v>74</v>

--- a/docs/StructureDefinition-DIPSLocation.xlsx
+++ b/docs/StructureDefinition-DIPSLocation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T19:39:02+00:00</t>
+    <t>2026-09-18T19:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSLocation.xlsx
+++ b/docs/StructureDefinition-DIPSLocation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T19:41:15+00:00</t>
+    <t>2026-09-29T03:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSLocation.xlsx
+++ b/docs/StructureDefinition-DIPSLocation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T03:57:01+00:00</t>
+    <t>2026-09-29T04:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
